--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\전달\2026-10-19_연구소_식이데이터계약\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8167BC-9502-4AD1-BBA5-114CC6AC37D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53DB155-A13A-4114-B03C-2DB05CD7F777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -18072,7 +18072,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DietGuide" displayName="DietGuide" ref="A1:D14" totalsRowShown="0" headerRowDxfId="247" dataDxfId="246">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DietGuide" displayName="DietGuide" ref="A13:D26" totalsRowShown="0" headerRowDxfId="247" dataDxfId="246">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="항목" dataDxfId="245"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="내용" dataDxfId="244"/>
@@ -18688,282 +18688,282 @@
     <col min="5" max="5" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="31">
+      <c r="A1" s="41" t="s">
+        <v>4785</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+    </row>
+    <row r="2" spans="1:4" ht="70">
+      <c r="A2" s="40" t="s">
+        <v>4820</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B4" s="34" t="s">
+        <v>4786</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="42">
+      <c r="A5" s="40" t="s">
+        <v>4787</v>
+      </c>
+      <c r="B5" s="40" t="s">
+        <v>4788</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>4789</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>4790</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="42">
+      <c r="A6" s="40" t="s">
+        <v>4791</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>4792</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>4793</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>4794</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="28">
+      <c r="A7" s="40" t="s">
+        <v>4795</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>4796</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>4797</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>4798</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="42">
+      <c r="A8" s="40" t="s">
+        <v>4799</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>4800</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>4801</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>4802</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="28">
+      <c r="A9" s="40" t="s">
+        <v>4803</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>4804</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>4805</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>4806</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="28">
+      <c r="A10" s="40" t="s">
+        <v>4807</v>
+      </c>
+      <c r="B10" s="40" t="s">
+        <v>4808</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>4809</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>4810</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="42">
+      <c r="A11" s="40" t="s">
+        <v>4821</v>
+      </c>
+      <c r="B11" s="40" t="s">
+        <v>4822</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>4823</v>
+      </c>
+      <c r="D11" s="40"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="25">
-      <c r="A2" s="3" t="s">
+    <row r="14" spans="1:4" ht="25">
+      <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="3" t="s">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="3" t="s">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="3" t="s">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6" spans="1:4" ht="25" customHeight="1">
-      <c r="A6" s="3" t="s">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="1:4" ht="25" customHeight="1">
+      <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B18" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="3" t="s">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" spans="1:4" ht="25" customHeight="1">
-      <c r="A8" s="3" t="s">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4" ht="25" customHeight="1">
+      <c r="A20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="3" t="s">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" spans="1:4" ht="26" customHeight="1">
-      <c r="A10" s="3" t="s">
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="1:4" ht="26" customHeight="1">
+      <c r="A22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="18" t="str">
+      <c r="B22" s="18" t="str">
         <f>"질문 "&amp;COUNTA(질문!A2:A100)&amp;", 선택지 "&amp;COUNTA(선택지!A2:A200)&amp;", 목표문구 "&amp;COUNTA(목표문구!A2:A999)&amp;", 노출조건 "&amp;COUNTA(노출조건!A2:A999)&amp;", 질환규칙 "&amp;COUNTA(질환규칙!A2:A100)&amp;", 상병코드조건 "&amp;COUNTA(상병코드조건!A2:A1000)&amp;", 설정 "&amp;COUNTA(설정!A2:A1000)&amp;" · 식후 가능 문구 "&amp;COUNTIF(노출조건!G2:G999,TRUE)&amp;" · 보류 문구 "&amp;COUNTIF(목표문구!C2:C999,"보류")</f>
         <v>질문 9, 선택지 27, 목표문구 403, 노출조건 403, 질환규칙 14, 상병코드조건 61, 설정 68 · 식후 가능 문구 99 · 보류 문구 0</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11" spans="1:4" ht="25" customHeight="1">
-      <c r="A11" s="3" t="s">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" ht="25" customHeight="1">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="3" t="s">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="1:4" ht="25" customHeight="1">
-      <c r="A13" s="3" t="s">
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="1:4" ht="25" customHeight="1">
+      <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B25" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A14" s="3" t="s">
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A26" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="6"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="1:4" ht="31">
-      <c r="A16" s="41" t="s">
-        <v>4785</v>
-      </c>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-    </row>
-    <row r="17" spans="1:4" ht="70">
-      <c r="A17" s="40" t="s">
-        <v>4820</v>
-      </c>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="34" t="s">
-        <v>4786</v>
-      </c>
-      <c r="C19" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="42">
-      <c r="A20" s="40" t="s">
-        <v>4787</v>
-      </c>
-      <c r="B20" s="40" t="s">
-        <v>4788</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>4789</v>
-      </c>
-      <c r="D20" s="40" t="s">
-        <v>4790</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="42">
-      <c r="A21" s="40" t="s">
-        <v>4791</v>
-      </c>
-      <c r="B21" s="40" t="s">
-        <v>4792</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>4793</v>
-      </c>
-      <c r="D21" s="40" t="s">
-        <v>4794</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="28">
-      <c r="A22" s="40" t="s">
-        <v>4795</v>
-      </c>
-      <c r="B22" s="40" t="s">
-        <v>4796</v>
-      </c>
-      <c r="C22" s="40" t="s">
-        <v>4797</v>
-      </c>
-      <c r="D22" s="40" t="s">
-        <v>4798</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="42">
-      <c r="A23" s="40" t="s">
-        <v>4799</v>
-      </c>
-      <c r="B23" s="40" t="s">
-        <v>4800</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>4801</v>
-      </c>
-      <c r="D23" s="40" t="s">
-        <v>4802</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="28">
-      <c r="A24" s="40" t="s">
-        <v>4803</v>
-      </c>
-      <c r="B24" s="40" t="s">
-        <v>4804</v>
-      </c>
-      <c r="C24" s="40" t="s">
-        <v>4805</v>
-      </c>
-      <c r="D24" s="40" t="s">
-        <v>4806</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="28">
-      <c r="A25" s="40" t="s">
-        <v>4807</v>
-      </c>
-      <c r="B25" s="40" t="s">
-        <v>4808</v>
-      </c>
-      <c r="C25" s="40" t="s">
-        <v>4809</v>
-      </c>
-      <c r="D25" s="40" t="s">
-        <v>4810</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="42">
-      <c r="A26" s="40" t="s">
-        <v>4821</v>
-      </c>
-      <c r="B26" s="40" t="s">
-        <v>4822</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>4823</v>
-      </c>
-      <c r="D26" s="40"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="6"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="6" t="s">

--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\전달\2026-10-19_연구소_식이데이터계약\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E6ECFD-4EB1-42FE-922D-2CB232F08C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DDF7BC-45EC-47CB-9510-10C5C9E7C2CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="먼저 읽기" sheetId="30" r:id="rId1"/>
+    <sheet name="안내" sheetId="30" r:id="rId1"/>
     <sheet name="테이블정의" sheetId="3" r:id="rId2"/>
     <sheet name="필드정의" sheetId="4" r:id="rId3"/>
     <sheet name="구현기준" sheetId="5" r:id="rId4"/>
@@ -14393,340 +14393,6 @@
   </si>
   <si>
     <t>참고</t>
-  </si>
-  <si>
-    <r>
-      <t>식이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>개발</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>전달</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>계약</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먼저</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>읽기</t>
-    </r>
-  </si>
-  <si>
-    <t>이 시트만 보면 됩니다. 읽는 순서는 ① 지금 연구소가 할 일 → ② 이 파일 기본 정보 → ③ 이 파일에서 바뀐 내용입니다. 맨 앞 「상태」 칸의 색 배지로 할 일을 구분합니다. 「반영 완료」 줄은 숨겨 두었습니다(행 번호 사이를 우클릭 → 숨기기 취소).</t>
-  </si>
-  <si>
-    <r>
-      <t>①</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지금</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>연구소가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>할</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관리자</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>콘솔</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> diet-1.1.1(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>현재</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적용</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>비교</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · 2026-10-19</t>
-    </r>
   </si>
   <si>
     <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「꼭 수정」 「권장」은 데이터를 바꿀 것, 「확인 필요」는 회신이 필요한 것입니다.</t>
@@ -15246,6 +14912,18 @@
       </rPr>
       <t>필요</t>
     </r>
+  </si>
+  <si>
+    <t>식이 개발 전달 데이터 계약 · 안내</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 시트만 보면 됩니다. 읽는 순서는 ① 연구소 전달용 → ② 이 파일 기본 정보 → ③ 이 파일에서 바뀐 내용입니다. 맨 앞 「상태」 칸의 색 배지로 할 일을 구분합니다. 「반영 완료」 줄은 숨겨 두었습니다(행 번호 사이를 우클릭 → 숨기기 취소).</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 연구소 전달용 · 관리자 콘솔 diet-1.1.1(현재 적용 중)과 비교 · 2026-10-19</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -15632,31 +15310,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -15674,20 +15337,35 @@
     <xf numFmtId="0" fontId="27" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -19416,531 +19094,543 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="50" t="s">
+        <v>4816</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+    </row>
+    <row r="2" spans="1:5" ht="34" customHeight="1">
+      <c r="A2" s="48" t="s">
+        <v>4817</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1">
+      <c r="A4" s="46" t="s">
+        <v>4818</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+    </row>
+    <row r="5" spans="1:5" ht="19" customHeight="1">
+      <c r="A5" s="48" t="s">
         <v>4774</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-    </row>
-    <row r="2" spans="1:5" ht="34" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+    </row>
+    <row r="6" spans="1:5" ht="20" customHeight="1">
+      <c r="A6" s="35" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B6" s="35" t="s">
         <v>4775</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
-      <c r="A4" s="38" t="s">
+      <c r="C6" s="35" t="s">
         <v>4776</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-    </row>
-    <row r="5" spans="1:5" ht="19" customHeight="1">
-      <c r="A5" s="37" t="s">
+      <c r="D6" s="35" t="s">
         <v>4777</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-    </row>
-    <row r="6" spans="1:5" ht="20" customHeight="1">
-      <c r="A6" s="40" t="s">
+      <c r="E6" s="35" t="s">
+        <v>4778</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="48" customHeight="1">
+      <c r="A7" s="38" t="s">
+        <v>4783</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>4779</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>4780</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>4781</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>4782</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="48" customHeight="1">
+      <c r="A8" s="40" t="s">
+        <v>4788</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>4784</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>4785</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>4786</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>4787</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="48" customHeight="1">
+      <c r="A9" s="41" t="s">
+        <v>4793</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>4789</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>4790</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>4791</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>4792</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="48" customHeight="1">
+      <c r="A10" s="41" t="s">
+        <v>4793</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>4794</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>4795</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>4796</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>4797</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="33" customHeight="1">
+      <c r="A11" s="41" t="s">
+        <v>4793</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>4798</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>4799</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>4800</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>4801</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="48" customHeight="1">
+      <c r="A12" s="42" t="s">
+        <v>4773</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>4802</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>4803</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>4804</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>4805</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="78" hidden="1" customHeight="1">
+      <c r="A13" s="43" t="s">
+        <v>4809</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>4806</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>4807</v>
+      </c>
+      <c r="D13" s="37" t="s">
+        <v>4808</v>
+      </c>
+      <c r="E13" s="37"/>
+    </row>
+    <row r="15" spans="1:5" ht="24" customHeight="1">
+      <c r="A15" s="46" t="s">
+        <v>4810</v>
+      </c>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+    </row>
+    <row r="16" spans="1:5" ht="20" customHeight="1">
+      <c r="B16" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+    </row>
+    <row r="17" spans="1:5" ht="18" customHeight="1">
+      <c r="B17" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+    </row>
+    <row r="18" spans="1:5" ht="18" customHeight="1">
+      <c r="B18" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+    </row>
+    <row r="19" spans="1:5" ht="18" customHeight="1">
+      <c r="B19" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+    </row>
+    <row r="20" spans="1:5" ht="18" customHeight="1">
+      <c r="B20" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+    </row>
+    <row r="21" spans="1:5" ht="18" customHeight="1">
+      <c r="B21" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+    </row>
+    <row r="22" spans="1:5" ht="18" customHeight="1">
+      <c r="B22" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+    </row>
+    <row r="23" spans="1:5" ht="18" customHeight="1">
+      <c r="B23" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+    </row>
+    <row r="24" spans="1:5" ht="18" customHeight="1">
+      <c r="B24" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+    </row>
+    <row r="25" spans="1:5" ht="18" customHeight="1">
+      <c r="B25" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="49" t="s">
+        <v>4811</v>
+      </c>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+    </row>
+    <row r="26" spans="1:5" ht="18" customHeight="1">
+      <c r="B26" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+    </row>
+    <row r="27" spans="1:5" ht="18" customHeight="1">
+      <c r="B27" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+    </row>
+    <row r="28" spans="1:5" ht="18" customHeight="1">
+      <c r="B28" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+    </row>
+    <row r="29" spans="1:5" ht="33" customHeight="1">
+      <c r="B29" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+    </row>
+    <row r="31" spans="1:5" ht="24" customHeight="1">
+      <c r="A31" s="46" t="s">
+        <v>4812</v>
+      </c>
+      <c r="B31" s="47"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+    </row>
+    <row r="32" spans="1:5" ht="34" customHeight="1">
+      <c r="A32" s="48" t="s">
+        <v>4813</v>
+      </c>
+      <c r="B32" s="48"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="48"/>
+    </row>
+    <row r="33" spans="1:5" ht="20" customHeight="1">
+      <c r="A33" s="35" t="s">
         <v>1050</v>
       </c>
-      <c r="B6" s="40" t="s">
-        <v>4778</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>4779</v>
-      </c>
-      <c r="D6" s="40" t="s">
-        <v>4780</v>
-      </c>
-      <c r="E6" s="40" t="s">
-        <v>4781</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="48" customHeight="1">
-      <c r="A7" s="43" t="s">
-        <v>4786</v>
-      </c>
-      <c r="B7" s="41" t="s">
-        <v>4782</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>4783</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>4784</v>
-      </c>
-      <c r="E7" s="41" t="s">
-        <v>4785</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="48" customHeight="1">
-      <c r="A8" s="45" t="s">
-        <v>4791</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>4787</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>4788</v>
-      </c>
-      <c r="D8" s="44" t="s">
-        <v>4789</v>
-      </c>
-      <c r="E8" s="44" t="s">
-        <v>4790</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="48" customHeight="1">
-      <c r="A9" s="46" t="s">
-        <v>4796</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>4792</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>4793</v>
-      </c>
-      <c r="D9" s="44" t="s">
-        <v>4794</v>
-      </c>
-      <c r="E9" s="44" t="s">
-        <v>4795</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="48" customHeight="1">
-      <c r="A10" s="46" t="s">
-        <v>4796</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>4797</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>4798</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>4799</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="33" customHeight="1">
-      <c r="A11" s="46" t="s">
-        <v>4796</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>4801</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>4802</v>
-      </c>
-      <c r="D11" s="44" t="s">
-        <v>4803</v>
-      </c>
-      <c r="E11" s="44" t="s">
-        <v>4804</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="48" customHeight="1">
-      <c r="A12" s="47" t="s">
-        <v>4773</v>
-      </c>
-      <c r="B12" s="44" t="s">
-        <v>4805</v>
-      </c>
-      <c r="C12" s="44" t="s">
-        <v>4806</v>
-      </c>
-      <c r="D12" s="44" t="s">
-        <v>4807</v>
-      </c>
-      <c r="E12" s="44" t="s">
-        <v>4808</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="78" hidden="1" customHeight="1">
-      <c r="A13" s="48" t="s">
-        <v>4812</v>
-      </c>
-      <c r="B13" s="42" t="s">
+      <c r="B33" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="35" t="s">
+        <v>4814</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="78" customHeight="1">
+      <c r="A34" s="38" t="s">
+        <v>4815</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>4769</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>4770</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>4771</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>4772</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="93" hidden="1" customHeight="1">
+      <c r="A35" s="44" t="s">
         <v>4809</v>
       </c>
-      <c r="C13" s="42" t="s">
-        <v>4810</v>
-      </c>
-      <c r="D13" s="42" t="s">
-        <v>4811</v>
-      </c>
-      <c r="E13" s="42"/>
-    </row>
-    <row r="15" spans="1:5" ht="24" customHeight="1">
-      <c r="A15" s="38" t="s">
-        <v>4813</v>
-      </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-    </row>
-    <row r="16" spans="1:5" ht="20" customHeight="1">
-      <c r="B16" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-    </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1">
-      <c r="B17" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-    </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1">
-      <c r="B18" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="50" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-    </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1">
-      <c r="B19" s="44" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="50" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-    </row>
-    <row r="20" spans="1:5" ht="18" customHeight="1">
-      <c r="B20" s="44" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-    </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1">
-      <c r="B21" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="50" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-    </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1">
-      <c r="B22" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-    </row>
-    <row r="23" spans="1:5" ht="18" customHeight="1">
-      <c r="B23" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-    </row>
-    <row r="24" spans="1:5" ht="18" customHeight="1">
-      <c r="B24" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-    </row>
-    <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="B25" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="50" t="s">
-        <v>4814</v>
-      </c>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-    </row>
-    <row r="26" spans="1:5" ht="18" customHeight="1">
-      <c r="B26" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-    </row>
-    <row r="27" spans="1:5" ht="18" customHeight="1">
-      <c r="B27" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-    </row>
-    <row r="28" spans="1:5" ht="18" customHeight="1">
-      <c r="B28" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-    </row>
-    <row r="29" spans="1:5" ht="33" customHeight="1">
-      <c r="B29" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-    </row>
-    <row r="31" spans="1:5" ht="24" customHeight="1">
-      <c r="A31" s="38" t="s">
-        <v>4815</v>
-      </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-    </row>
-    <row r="32" spans="1:5" ht="34" customHeight="1">
-      <c r="A32" s="37" t="s">
-        <v>4816</v>
-      </c>
-      <c r="B32" s="37"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-    </row>
-    <row r="33" spans="1:5" ht="20" customHeight="1">
-      <c r="A33" s="40" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B33" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33" s="40" t="s">
-        <v>4817</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="78" customHeight="1">
-      <c r="A34" s="43" t="s">
-        <v>4818</v>
-      </c>
-      <c r="B34" s="41" t="s">
-        <v>4769</v>
-      </c>
-      <c r="C34" s="41" t="s">
-        <v>4770</v>
-      </c>
-      <c r="D34" s="41" t="s">
-        <v>4771</v>
-      </c>
-      <c r="E34" s="41" t="s">
-        <v>4772</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A35" s="53" t="s">
-        <v>4812</v>
-      </c>
-      <c r="B35" s="44" t="s">
+      <c r="B35" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="44" t="s">
+      <c r="C35" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="44" t="s">
+      <c r="D35" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="E35" s="44" t="s">
+      <c r="E35" s="39" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="108" hidden="1" customHeight="1">
-      <c r="A36" s="53" t="s">
-        <v>4812</v>
-      </c>
-      <c r="B36" s="44" t="s">
+      <c r="A36" s="44" t="s">
+        <v>4809</v>
+      </c>
+      <c r="B36" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="44" t="s">
+      <c r="C36" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="D36" s="44" t="s">
+      <c r="D36" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="E36" s="44" t="s">
+      <c r="E36" s="39" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="63" hidden="1" customHeight="1">
-      <c r="A37" s="53" t="s">
-        <v>4812</v>
-      </c>
-      <c r="B37" s="44" t="s">
+      <c r="A37" s="44" t="s">
+        <v>4809</v>
+      </c>
+      <c r="B37" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="44" t="s">
+      <c r="C37" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="44" t="s">
+      <c r="D37" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="E37" s="44" t="s">
+      <c r="E37" s="39" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="123" hidden="1" customHeight="1">
-      <c r="A38" s="53" t="s">
-        <v>4812</v>
-      </c>
-      <c r="B38" s="44" t="s">
+      <c r="A38" s="44" t="s">
+        <v>4809</v>
+      </c>
+      <c r="B38" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="44" t="s">
+      <c r="C38" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="D38" s="44" t="s">
+      <c r="D38" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E38" s="44" t="s">
+      <c r="E38" s="39" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="303" hidden="1" customHeight="1">
-      <c r="A39" s="53" t="s">
-        <v>4812</v>
-      </c>
-      <c r="B39" s="44" t="s">
+      <c r="A39" s="44" t="s">
+        <v>4809</v>
+      </c>
+      <c r="B39" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="44" t="s">
+      <c r="C39" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="D39" s="44" t="s">
+      <c r="D39" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="E39" s="44" t="s">
+      <c r="E39" s="39" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A40" s="53" t="s">
-        <v>4812</v>
-      </c>
-      <c r="B40" s="44" t="s">
+      <c r="A40" s="44" t="s">
+        <v>4809</v>
+      </c>
+      <c r="B40" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="44" t="s">
+      <c r="C40" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="44" t="s">
+      <c r="D40" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="E40" s="44" t="s">
+      <c r="E40" s="39" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="78" hidden="1" customHeight="1">
-      <c r="A41" s="53" t="s">
-        <v>4812</v>
-      </c>
-      <c r="B41" s="44" t="s">
+      <c r="A41" s="44" t="s">
+        <v>4809</v>
+      </c>
+      <c r="B41" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="44" t="s">
+      <c r="C41" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="D41" s="44" t="s">
+      <c r="D41" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="E41" s="44" t="s">
+      <c r="E41" s="39" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A42" s="53" t="s">
-        <v>4812</v>
-      </c>
-      <c r="B42" s="44" t="s">
+      <c r="A42" s="44" t="s">
+        <v>4809</v>
+      </c>
+      <c r="B42" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="C42" s="44" t="s">
+      <c r="C42" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="44" t="s">
+      <c r="D42" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E42" s="44" t="s">
+      <c r="E42" s="39" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A43" s="48" t="s">
-        <v>4812</v>
-      </c>
-      <c r="B43" s="42" t="s">
+      <c r="A43" s="43" t="s">
+        <v>4809</v>
+      </c>
+      <c r="B43" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="C43" s="42" t="s">
+      <c r="C43" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="D43" s="42" t="s">
+      <c r="D43" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="E43" s="42" t="s">
+      <c r="E43" s="37" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A32:E32"/>
@@ -19950,18 +19640,6 @@
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="C16:E16"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\전달\2026-10-19_연구소_식이데이터계약\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DDF7BC-45EC-47CB-9510-10C5C9E7C2CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E6FB87-3092-4667-8ED2-523620F47090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14395,9 +14395,6 @@
     <t>참고</t>
   </si>
   <si>
-    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「꼭 수정」 「권장」은 데이터를 바꿀 것, 「확인 필요」는 회신이 필요한 것입니다.</t>
-  </si>
-  <si>
     <r>
       <t>할</t>
     </r>
@@ -14495,30 +14492,6 @@
   </si>
   <si>
     <t>policy goal_history_days · 설정 CFG-065 · 설정파라미터 CFG-065 · 검증규칙 V-45</t>
-  </si>
-  <si>
-    <r>
-      <t>꼭</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>수정</t>
-    </r>
   </si>
   <si>
     <t>목표 단계 오르기 정책값</t>
@@ -14923,6 +14896,14 @@
   </si>
   <si>
     <t>① 연구소 전달용 · 관리자 콘솔 diet-1.1.1(현재 적용 중)과 비교 · 2026-10-19</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「수정 요청」 「권장」은 데이터를 바꿀 것, 「확인 필요」는 회신이 필요한 것입니다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정 요청</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -15340,18 +15321,6 @@
     <xf numFmtId="0" fontId="27" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -15361,10 +15330,22 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -19094,17 +19075,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="50" t="s">
-        <v>4816</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
+      <c r="A1" s="46" t="s">
+        <v>4814</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
     </row>
     <row r="2" spans="1:5" ht="34" customHeight="1">
       <c r="A2" s="48" t="s">
-        <v>4817</v>
+        <v>4815</v>
       </c>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
@@ -19112,17 +19093,17 @@
       <c r="E2" s="48"/>
     </row>
     <row r="4" spans="1:5" ht="24" customHeight="1">
-      <c r="A4" s="46" t="s">
-        <v>4818</v>
-      </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
+      <c r="A4" s="49" t="s">
+        <v>4816</v>
+      </c>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
     </row>
     <row r="5" spans="1:5" ht="19" customHeight="1">
       <c r="A5" s="48" t="s">
-        <v>4774</v>
+        <v>4817</v>
       </c>
       <c r="B5" s="48"/>
       <c r="C5" s="48"/>
@@ -19134,101 +19115,101 @@
         <v>1050</v>
       </c>
       <c r="B6" s="35" t="s">
+        <v>4774</v>
+      </c>
+      <c r="C6" s="35" t="s">
         <v>4775</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="D6" s="35" t="s">
         <v>4776</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="E6" s="35" t="s">
         <v>4777</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>4778</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="48" customHeight="1">
       <c r="A7" s="38" t="s">
-        <v>4783</v>
+        <v>4818</v>
       </c>
       <c r="B7" s="36" t="s">
+        <v>4778</v>
+      </c>
+      <c r="C7" s="36" t="s">
         <v>4779</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="D7" s="36" t="s">
         <v>4780</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="E7" s="36" t="s">
         <v>4781</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>4782</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="48" customHeight="1">
       <c r="A8" s="40" t="s">
-        <v>4788</v>
+        <v>4786</v>
       </c>
       <c r="B8" s="39" t="s">
+        <v>4782</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>4783</v>
+      </c>
+      <c r="D8" s="39" t="s">
         <v>4784</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="E8" s="39" t="s">
         <v>4785</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>4786</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>4787</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="48" customHeight="1">
       <c r="A9" s="41" t="s">
-        <v>4793</v>
+        <v>4791</v>
       </c>
       <c r="B9" s="39" t="s">
+        <v>4787</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>4788</v>
+      </c>
+      <c r="D9" s="39" t="s">
         <v>4789</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="E9" s="39" t="s">
         <v>4790</v>
-      </c>
-      <c r="D9" s="39" t="s">
-        <v>4791</v>
-      </c>
-      <c r="E9" s="39" t="s">
-        <v>4792</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="48" customHeight="1">
       <c r="A10" s="41" t="s">
+        <v>4791</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>4792</v>
+      </c>
+      <c r="C10" s="39" t="s">
         <v>4793</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="D10" s="39" t="s">
         <v>4794</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="E10" s="39" t="s">
         <v>4795</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>4796</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>4797</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="33" customHeight="1">
       <c r="A11" s="41" t="s">
-        <v>4793</v>
+        <v>4791</v>
       </c>
       <c r="B11" s="39" t="s">
+        <v>4796</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>4797</v>
+      </c>
+      <c r="D11" s="39" t="s">
         <v>4798</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="E11" s="39" t="s">
         <v>4799</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>4800</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>4801</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="48" customHeight="1">
@@ -19236,194 +19217,194 @@
         <v>4773</v>
       </c>
       <c r="B12" s="39" t="s">
+        <v>4800</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>4801</v>
+      </c>
+      <c r="D12" s="39" t="s">
         <v>4802</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="E12" s="39" t="s">
         <v>4803</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>4804</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>4805</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="78" hidden="1" customHeight="1">
       <c r="A13" s="43" t="s">
-        <v>4809</v>
+        <v>4807</v>
       </c>
       <c r="B13" s="37" t="s">
+        <v>4804</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>4805</v>
+      </c>
+      <c r="D13" s="37" t="s">
         <v>4806</v>
       </c>
-      <c r="C13" s="37" t="s">
-        <v>4807</v>
-      </c>
-      <c r="D13" s="37" t="s">
+      <c r="E13" s="37"/>
+    </row>
+    <row r="15" spans="1:5" ht="24" customHeight="1">
+      <c r="A15" s="49" t="s">
         <v>4808</v>
       </c>
-      <c r="E13" s="37"/>
-    </row>
-    <row r="15" spans="1:5" ht="24" customHeight="1">
-      <c r="A15" s="46" t="s">
-        <v>4810</v>
-      </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1">
       <c r="B16" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="C16" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1">
       <c r="B17" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1">
       <c r="B18" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="49" t="s">
+      <c r="C18" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1">
       <c r="B19" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="49" t="s">
+      <c r="C19" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1">
       <c r="B20" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="49" t="s">
+      <c r="C20" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1">
       <c r="B21" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="49" t="s">
+      <c r="C21" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1">
       <c r="B22" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="C22" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1">
       <c r="B23" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1">
       <c r="B24" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1">
       <c r="B25" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="49" t="s">
-        <v>4811</v>
-      </c>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
+      <c r="C25" s="45" t="s">
+        <v>4809</v>
+      </c>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1">
       <c r="B26" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C26" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1">
       <c r="B27" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="49" t="s">
+      <c r="C27" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
     </row>
     <row r="28" spans="1:5" ht="18" customHeight="1">
       <c r="B28" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="49" t="s">
+      <c r="C28" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
     </row>
     <row r="29" spans="1:5" ht="33" customHeight="1">
       <c r="B29" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="45" t="s">
+      <c r="C29" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
     </row>
     <row r="31" spans="1:5" ht="24" customHeight="1">
-      <c r="A31" s="46" t="s">
-        <v>4812</v>
-      </c>
-      <c r="B31" s="47"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
+      <c r="A31" s="49" t="s">
+        <v>4810</v>
+      </c>
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
     </row>
     <row r="32" spans="1:5" ht="34" customHeight="1">
       <c r="A32" s="48" t="s">
-        <v>4813</v>
+        <v>4811</v>
       </c>
       <c r="B32" s="48"/>
       <c r="C32" s="48"/>
@@ -19444,12 +19425,12 @@
         <v>28</v>
       </c>
       <c r="E33" s="35" t="s">
-        <v>4814</v>
+        <v>4812</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="78" customHeight="1">
       <c r="A34" s="38" t="s">
-        <v>4815</v>
+        <v>4813</v>
       </c>
       <c r="B34" s="36" t="s">
         <v>4769</v>
@@ -19466,7 +19447,7 @@
     </row>
     <row r="35" spans="1:5" ht="93" hidden="1" customHeight="1">
       <c r="A35" s="44" t="s">
-        <v>4809</v>
+        <v>4807</v>
       </c>
       <c r="B35" s="39" t="s">
         <v>59</v>
@@ -19483,7 +19464,7 @@
     </row>
     <row r="36" spans="1:5" ht="108" hidden="1" customHeight="1">
       <c r="A36" s="44" t="s">
-        <v>4809</v>
+        <v>4807</v>
       </c>
       <c r="B36" s="39" t="s">
         <v>56</v>
@@ -19500,7 +19481,7 @@
     </row>
     <row r="37" spans="1:5" ht="63" hidden="1" customHeight="1">
       <c r="A37" s="44" t="s">
-        <v>4809</v>
+        <v>4807</v>
       </c>
       <c r="B37" s="39" t="s">
         <v>53</v>
@@ -19517,7 +19498,7 @@
     </row>
     <row r="38" spans="1:5" ht="123" hidden="1" customHeight="1">
       <c r="A38" s="44" t="s">
-        <v>4809</v>
+        <v>4807</v>
       </c>
       <c r="B38" s="39" t="s">
         <v>49</v>
@@ -19534,7 +19515,7 @@
     </row>
     <row r="39" spans="1:5" ht="303" hidden="1" customHeight="1">
       <c r="A39" s="44" t="s">
-        <v>4809</v>
+        <v>4807</v>
       </c>
       <c r="B39" s="39" t="s">
         <v>45</v>
@@ -19551,7 +19532,7 @@
     </row>
     <row r="40" spans="1:5" ht="93" hidden="1" customHeight="1">
       <c r="A40" s="44" t="s">
-        <v>4809</v>
+        <v>4807</v>
       </c>
       <c r="B40" s="39" t="s">
         <v>41</v>
@@ -19568,7 +19549,7 @@
     </row>
     <row r="41" spans="1:5" ht="78" hidden="1" customHeight="1">
       <c r="A41" s="44" t="s">
-        <v>4809</v>
+        <v>4807</v>
       </c>
       <c r="B41" s="39" t="s">
         <v>37</v>
@@ -19585,7 +19566,7 @@
     </row>
     <row r="42" spans="1:5" ht="93" hidden="1" customHeight="1">
       <c r="A42" s="44" t="s">
-        <v>4809</v>
+        <v>4807</v>
       </c>
       <c r="B42" s="39" t="s">
         <v>33</v>
@@ -19602,7 +19583,7 @@
     </row>
     <row r="43" spans="1:5" ht="93" hidden="1" customHeight="1">
       <c r="A43" s="43" t="s">
-        <v>4809</v>
+        <v>4807</v>
       </c>
       <c r="B43" s="37" t="s">
         <v>29</v>
@@ -19619,6 +19600,15 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
@@ -19631,15 +19621,6 @@
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\전달\2026-10-19_연구소_식이데이터계약\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E6FB87-3092-4667-8ED2-523620F47090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD587AC8-3C13-4A9A-87B7-B533493DA8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15467" uniqueCount="4819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15467" uniqueCount="4820">
   <si>
     <t>항목</t>
   </si>
@@ -14519,30 +14519,6 @@
   </si>
   <si>
     <t>서버 규칙 문서 11.1 · 문구 사용 이력</t>
-  </si>
-  <si>
-    <r>
-      <t>확인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF7F6000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF7F6000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>필요</t>
-    </r>
   </si>
   <si>
     <t>규칙 문서 8.3 문구 고르기 설명</t>
@@ -14899,11 +14875,19 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「수정 요청」 「권장」은 데이터를 바꿀 것, 「확인 필요」는 회신이 필요한 것입니다.</t>
+    <t>수정 요청</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>수정 요청</t>
+    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「수정 요청」 「권장」은 데이터를 바꿀 것, 「답변 요청」은 회신만 주면 되는 것, 「문서 수정 요청」은 서버 규칙 문서를 고칠 것입니다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>답변 요청</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>문서 수정 요청</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -15063,13 +15047,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF7F6000"/>
-      <name val="Carlito"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FF404040"/>
       <name val="Carlito"/>
     </font>
@@ -15086,8 +15063,14 @@
       <name val="Carlito"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF5B3B8C"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -15152,6 +15135,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -15201,7 +15190,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -15312,14 +15301,26 @@
     <xf numFmtId="0" fontId="24" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -15330,23 +15331,14 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -19075,17 +19067,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="46" t="s">
-        <v>4814</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
+      <c r="A1" s="50" t="s">
+        <v>4813</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" ht="34" customHeight="1">
       <c r="A2" s="48" t="s">
-        <v>4815</v>
+        <v>4814</v>
       </c>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
@@ -19093,13 +19085,13 @@
       <c r="E2" s="48"/>
     </row>
     <row r="4" spans="1:5" ht="24" customHeight="1">
-      <c r="A4" s="49" t="s">
-        <v>4816</v>
-      </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
+      <c r="A4" s="46" t="s">
+        <v>4815</v>
+      </c>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
     </row>
     <row r="5" spans="1:5" ht="19" customHeight="1">
       <c r="A5" s="48" t="s">
@@ -19129,7 +19121,7 @@
     </row>
     <row r="7" spans="1:5" ht="48" customHeight="1">
       <c r="A7" s="38" t="s">
-        <v>4818</v>
+        <v>4816</v>
       </c>
       <c r="B7" s="36" t="s">
         <v>4778</v>
@@ -19163,7 +19155,7 @@
     </row>
     <row r="9" spans="1:5" ht="48" customHeight="1">
       <c r="A9" s="41" t="s">
-        <v>4791</v>
+        <v>4818</v>
       </c>
       <c r="B9" s="39" t="s">
         <v>4787</v>
@@ -19179,37 +19171,37 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="48" customHeight="1">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="54" t="s">
+        <v>4819</v>
+      </c>
+      <c r="B10" s="39" t="s">
         <v>4791</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="C10" s="39" t="s">
         <v>4792</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="D10" s="39" t="s">
         <v>4793</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="E10" s="39" t="s">
         <v>4794</v>
       </c>
-      <c r="E10" s="39" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="33" customHeight="1">
+      <c r="A11" s="54" t="s">
+        <v>4819</v>
+      </c>
+      <c r="B11" s="39" t="s">
         <v>4795</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="33" customHeight="1">
-      <c r="A11" s="41" t="s">
-        <v>4791</v>
-      </c>
-      <c r="B11" s="39" t="s">
+      <c r="C11" s="39" t="s">
         <v>4796</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="D11" s="39" t="s">
         <v>4797</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="E11" s="39" t="s">
         <v>4798</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>4799</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="48" customHeight="1">
@@ -19217,194 +19209,194 @@
         <v>4773</v>
       </c>
       <c r="B12" s="39" t="s">
+        <v>4799</v>
+      </c>
+      <c r="C12" s="39" t="s">
         <v>4800</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="D12" s="39" t="s">
         <v>4801</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="E12" s="39" t="s">
         <v>4802</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>4803</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="78" hidden="1" customHeight="1">
       <c r="A13" s="43" t="s">
+        <v>4806</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>4803</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>4804</v>
+      </c>
+      <c r="D13" s="37" t="s">
+        <v>4805</v>
+      </c>
+      <c r="E13" s="37"/>
+    </row>
+    <row r="15" spans="1:5" ht="24" customHeight="1">
+      <c r="A15" s="46" t="s">
         <v>4807</v>
       </c>
-      <c r="B13" s="37" t="s">
-        <v>4804</v>
-      </c>
-      <c r="C13" s="37" t="s">
-        <v>4805</v>
-      </c>
-      <c r="D13" s="37" t="s">
-        <v>4806</v>
-      </c>
-      <c r="E13" s="37"/>
-    </row>
-    <row r="15" spans="1:5" ht="24" customHeight="1">
-      <c r="A15" s="49" t="s">
-        <v>4808</v>
-      </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1">
       <c r="B16" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1">
       <c r="B17" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="52" t="s">
+      <c r="C17" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1">
       <c r="B18" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="45" t="s">
+      <c r="C18" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1">
       <c r="B19" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="45" t="s">
+      <c r="C19" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1">
       <c r="B20" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C20" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1">
       <c r="B21" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="45" t="s">
+      <c r="C21" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1">
       <c r="B22" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="45" t="s">
+      <c r="C22" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1">
       <c r="B23" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="45" t="s">
+      <c r="C23" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1">
       <c r="B24" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="45" t="s">
+      <c r="C24" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1">
       <c r="B25" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="45" t="s">
-        <v>4809</v>
-      </c>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
+      <c r="C25" s="49" t="s">
+        <v>4808</v>
+      </c>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1">
       <c r="B26" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="45" t="s">
+      <c r="C26" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1">
       <c r="B27" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="45" t="s">
+      <c r="C27" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
     </row>
     <row r="28" spans="1:5" ht="18" customHeight="1">
       <c r="B28" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="45" t="s">
+      <c r="C28" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
     </row>
     <row r="29" spans="1:5" ht="33" customHeight="1">
       <c r="B29" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="53" t="s">
+      <c r="C29" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
     </row>
     <row r="31" spans="1:5" ht="24" customHeight="1">
-      <c r="A31" s="49" t="s">
-        <v>4810</v>
-      </c>
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
+      <c r="A31" s="46" t="s">
+        <v>4809</v>
+      </c>
+      <c r="B31" s="47"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
     </row>
     <row r="32" spans="1:5" ht="34" customHeight="1">
       <c r="A32" s="48" t="s">
-        <v>4811</v>
+        <v>4810</v>
       </c>
       <c r="B32" s="48"/>
       <c r="C32" s="48"/>
@@ -19425,12 +19417,12 @@
         <v>28</v>
       </c>
       <c r="E33" s="35" t="s">
-        <v>4812</v>
+        <v>4811</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="78" customHeight="1">
       <c r="A34" s="38" t="s">
-        <v>4813</v>
+        <v>4812</v>
       </c>
       <c r="B34" s="36" t="s">
         <v>4769</v>
@@ -19447,7 +19439,7 @@
     </row>
     <row r="35" spans="1:5" ht="93" hidden="1" customHeight="1">
       <c r="A35" s="44" t="s">
-        <v>4807</v>
+        <v>4806</v>
       </c>
       <c r="B35" s="39" t="s">
         <v>59</v>
@@ -19464,7 +19456,7 @@
     </row>
     <row r="36" spans="1:5" ht="108" hidden="1" customHeight="1">
       <c r="A36" s="44" t="s">
-        <v>4807</v>
+        <v>4806</v>
       </c>
       <c r="B36" s="39" t="s">
         <v>56</v>
@@ -19481,7 +19473,7 @@
     </row>
     <row r="37" spans="1:5" ht="63" hidden="1" customHeight="1">
       <c r="A37" s="44" t="s">
-        <v>4807</v>
+        <v>4806</v>
       </c>
       <c r="B37" s="39" t="s">
         <v>53</v>
@@ -19498,7 +19490,7 @@
     </row>
     <row r="38" spans="1:5" ht="123" hidden="1" customHeight="1">
       <c r="A38" s="44" t="s">
-        <v>4807</v>
+        <v>4806</v>
       </c>
       <c r="B38" s="39" t="s">
         <v>49</v>
@@ -19515,7 +19507,7 @@
     </row>
     <row r="39" spans="1:5" ht="303" hidden="1" customHeight="1">
       <c r="A39" s="44" t="s">
-        <v>4807</v>
+        <v>4806</v>
       </c>
       <c r="B39" s="39" t="s">
         <v>45</v>
@@ -19532,7 +19524,7 @@
     </row>
     <row r="40" spans="1:5" ht="93" hidden="1" customHeight="1">
       <c r="A40" s="44" t="s">
-        <v>4807</v>
+        <v>4806</v>
       </c>
       <c r="B40" s="39" t="s">
         <v>41</v>
@@ -19549,7 +19541,7 @@
     </row>
     <row r="41" spans="1:5" ht="78" hidden="1" customHeight="1">
       <c r="A41" s="44" t="s">
-        <v>4807</v>
+        <v>4806</v>
       </c>
       <c r="B41" s="39" t="s">
         <v>37</v>
@@ -19566,7 +19558,7 @@
     </row>
     <row r="42" spans="1:5" ht="93" hidden="1" customHeight="1">
       <c r="A42" s="44" t="s">
-        <v>4807</v>
+        <v>4806</v>
       </c>
       <c r="B42" s="39" t="s">
         <v>33</v>
@@ -19583,7 +19575,7 @@
     </row>
     <row r="43" spans="1:5" ht="93" hidden="1" customHeight="1">
       <c r="A43" s="43" t="s">
-        <v>4807</v>
+        <v>4806</v>
       </c>
       <c r="B43" s="37" t="s">
         <v>29</v>
@@ -19600,15 +19592,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
@@ -19621,6 +19604,15 @@
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\전달\2026-10-19_연구소_식이데이터계약\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD587AC8-3C13-4A9A-87B7-B533493DA8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3448D1F5-D7D0-4EC9-A937-1CA55CE1DD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15467" uniqueCount="4820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15447" uniqueCount="4801">
   <si>
     <t>항목</t>
   </si>
@@ -14390,9 +14390,6 @@
   </si>
   <si>
     <t>설정 CFG-065 · 설정파라미터 CFG-065 · 검증규칙 V-45</t>
-  </si>
-  <si>
-    <t>참고</t>
   </si>
   <si>
     <r>
@@ -14507,54 +14504,6 @@
   </si>
   <si>
     <t>권장</t>
-  </si>
-  <si>
-    <t>버전이 바뀔 때 문구 사용 이력</t>
-  </si>
-  <si>
-    <t>규칙 문서 11.1: 버전이 바뀌면 문구 사용 이력도 새로 시작 → 새 버전마다 모든 사용자가 첫 문구부터 다시 봄</t>
-  </si>
-  <si>
-    <t>문구 내용이 같은 줄(문구 ID · 문구 버전이 같은 줄)은 이력을 이어 볼 수 있는지 회신</t>
-  </si>
-  <si>
-    <t>서버 규칙 문서 11.1 · 문구 사용 이력</t>
-  </si>
-  <si>
-    <t>규칙 문서 8.3 문구 고르기 설명</t>
-  </si>
-  <si>
-    <t>「최근 30일 안 쓴 문구 → 오래전에 쓴 문구 → 데이터 순서」로 적혀 「안 쓴 문구가 먼저」로 읽힘</t>
-  </si>
-  <si>
-    <t>실제 동작대로 고침: 조회 기간 밖 문구와 안 쓴 문구를 같이 놓고 데이터 순서로 고름. 조회 기간 마지막 날(정확히 30일 전)에 쓴 문구도 「최근」으로 봄</t>
-  </si>
-  <si>
-    <t>서버 규칙 문서 8.3</t>
-  </si>
-  <si>
-    <t>규칙 문서 예시</t>
-  </si>
-  <si>
-    <t>8.4 · 5장 예시가 1.0.4 기준</t>
-  </si>
-  <si>
-    <t>1.1.1 기준으로 고침(예: 「국 대신 나물 반찬」은 채소 기본 단계, 새벽 3시에 「내일 채소 꺼내 두기」가 나옴)</t>
-  </si>
-  <si>
-    <t>서버 규칙 문서 5.4 · 8.4</t>
-  </si>
-  <si>
-    <t>영어 사용자 긴 문장 · 이유</t>
-  </si>
-  <si>
-    <t>title_text_full_context_en · reason_text_en 403개 모두 비어 있어 영어 목표 카드에 짧은 문구만 나옴</t>
-  </si>
-  <si>
-    <t>영문 번역은 우리가 정리해 다음에 전달함. 이번에 바꿀 것 없음</t>
-  </si>
-  <si>
-    <t>goal_phrases title_text_full_context_en · reason_text_en</t>
   </si>
   <si>
     <t>나머지</t>
@@ -14879,15 +14828,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「수정 요청」 「권장」은 데이터를 바꿀 것, 「답변 요청」은 회신만 주면 되는 것, 「문서 수정 요청」은 서버 규칙 문서를 고칠 것입니다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>답변 요청</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>문서 수정 요청</t>
+    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「수정 요청」은 꼭 바꿀 것, 「권장」은 바꾸면 좋은 것입니다.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -14898,7 +14839,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -15041,18 +14982,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF7F6000"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF404040"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FF375623"/>
       <name val="Carlito"/>
     </font>
@@ -15063,14 +14992,8 @@
       <name val="Carlito"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF5B3B8C"/>
-      <name val="Carlito"/>
-    </font>
   </fonts>
-  <fills count="13">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -15101,18 +15024,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDEDED"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -15132,12 +15043,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4DFEC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -15190,7 +15095,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -15280,7 +15185,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -15295,32 +15200,14 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -15331,14 +15218,23 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -19055,7 +18951,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="11.58203125" style="34" customWidth="1"/>
@@ -19067,552 +18963,484 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="50" t="s">
-        <v>4813</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
+      <c r="A1" s="44" t="s">
+        <v>4796</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
     </row>
     <row r="2" spans="1:5" ht="34" customHeight="1">
-      <c r="A2" s="48" t="s">
-        <v>4814</v>
-      </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
+      <c r="A2" s="46" t="s">
+        <v>4797</v>
+      </c>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
     </row>
     <row r="4" spans="1:5" ht="24" customHeight="1">
-      <c r="A4" s="46" t="s">
-        <v>4815</v>
-      </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
+      <c r="A4" s="47" t="s">
+        <v>4798</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
     </row>
     <row r="5" spans="1:5" ht="19" customHeight="1">
-      <c r="A5" s="48" t="s">
-        <v>4817</v>
-      </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
+      <c r="A5" s="46" t="s">
+        <v>4800</v>
+      </c>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
     </row>
     <row r="6" spans="1:5" ht="20" customHeight="1">
       <c r="A6" s="35" t="s">
         <v>1050</v>
       </c>
       <c r="B6" s="35" t="s">
+        <v>4773</v>
+      </c>
+      <c r="C6" s="35" t="s">
         <v>4774</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="D6" s="35" t="s">
         <v>4775</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="E6" s="35" t="s">
         <v>4776</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>4777</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="48" customHeight="1">
       <c r="A7" s="38" t="s">
-        <v>4816</v>
+        <v>4799</v>
       </c>
       <c r="B7" s="36" t="s">
+        <v>4777</v>
+      </c>
+      <c r="C7" s="36" t="s">
         <v>4778</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="D7" s="36" t="s">
         <v>4779</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="E7" s="36" t="s">
         <v>4780</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>4781</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="48" customHeight="1">
       <c r="A8" s="40" t="s">
+        <v>4785</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>4781</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>4782</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>4783</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="78" hidden="1" customHeight="1">
+      <c r="A9" s="41" t="s">
+        <v>4789</v>
+      </c>
+      <c r="B9" s="37" t="s">
         <v>4786</v>
       </c>
-      <c r="B8" s="39" t="s">
-        <v>4782</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>4783</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>4784</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>4785</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="48" customHeight="1">
-      <c r="A9" s="41" t="s">
-        <v>4818</v>
-      </c>
-      <c r="B9" s="39" t="s">
+      <c r="C9" s="37" t="s">
         <v>4787</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="D9" s="37" t="s">
         <v>4788</v>
       </c>
-      <c r="D9" s="39" t="s">
-        <v>4789</v>
-      </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="37"/>
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1">
+      <c r="A11" s="47" t="s">
         <v>4790</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="48" customHeight="1">
-      <c r="A10" s="54" t="s">
-        <v>4819</v>
-      </c>
-      <c r="B10" s="39" t="s">
-        <v>4791</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>4792</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>4793</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>4794</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="33" customHeight="1">
-      <c r="A11" s="54" t="s">
-        <v>4819</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>4795</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>4796</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>4797</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>4798</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="48" customHeight="1">
-      <c r="A12" s="42" t="s">
-        <v>4773</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>4799</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>4800</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>4801</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>4802</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="78" hidden="1" customHeight="1">
-      <c r="A13" s="43" t="s">
-        <v>4806</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>4803</v>
-      </c>
-      <c r="C13" s="37" t="s">
-        <v>4804</v>
-      </c>
-      <c r="D13" s="37" t="s">
-        <v>4805</v>
-      </c>
-      <c r="E13" s="37"/>
-    </row>
-    <row r="15" spans="1:5" ht="24" customHeight="1">
-      <c r="A15" s="46" t="s">
-        <v>4807</v>
-      </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-    </row>
-    <row r="16" spans="1:5" ht="20" customHeight="1">
-      <c r="B16" s="35" t="s">
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+    </row>
+    <row r="12" spans="1:5" ht="20" customHeight="1">
+      <c r="B12" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="C12" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+    </row>
+    <row r="13" spans="1:5" ht="18" customHeight="1">
+      <c r="B13" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+    </row>
+    <row r="14" spans="1:5" ht="18" customHeight="1">
+      <c r="B14" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+    </row>
+    <row r="15" spans="1:5" ht="18" customHeight="1">
+      <c r="B15" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+    </row>
+    <row r="16" spans="1:5" ht="18" customHeight="1">
+      <c r="B16" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1">
-      <c r="B17" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="53" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
+      <c r="B17" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1">
       <c r="B18" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1">
       <c r="B19" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
+        <v>14</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1">
       <c r="B20" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
+        <v>16</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1">
       <c r="B21" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
+        <v>18</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>4791</v>
+      </c>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1">
       <c r="B22" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
+        <v>19</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1">
       <c r="B23" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
+        <v>21</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1">
       <c r="B24" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-    </row>
-    <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="B25" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="49" t="s">
-        <v>4808</v>
-      </c>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-    </row>
-    <row r="26" spans="1:5" ht="18" customHeight="1">
-      <c r="B26" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-    </row>
-    <row r="27" spans="1:5" ht="18" customHeight="1">
-      <c r="B27" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-    </row>
-    <row r="28" spans="1:5" ht="18" customHeight="1">
-      <c r="B28" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="49" t="s">
+      <c r="C24" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-    </row>
-    <row r="29" spans="1:5" ht="33" customHeight="1">
-      <c r="B29" s="37" t="s">
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+    </row>
+    <row r="25" spans="1:5" ht="33" customHeight="1">
+      <c r="B25" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="45" t="s">
+      <c r="C25" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-    </row>
-    <row r="31" spans="1:5" ht="24" customHeight="1">
-      <c r="A31" s="46" t="s">
-        <v>4809</v>
-      </c>
-      <c r="B31" s="47"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-    </row>
-    <row r="32" spans="1:5" ht="34" customHeight="1">
-      <c r="A32" s="48" t="s">
-        <v>4810</v>
-      </c>
-      <c r="B32" s="48"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-    </row>
-    <row r="33" spans="1:5" ht="20" customHeight="1">
-      <c r="A33" s="35" t="s">
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+    </row>
+    <row r="27" spans="1:5" ht="24" customHeight="1">
+      <c r="A27" s="47" t="s">
+        <v>4792</v>
+      </c>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+    </row>
+    <row r="28" spans="1:5" ht="34" customHeight="1">
+      <c r="A28" s="46" t="s">
+        <v>4793</v>
+      </c>
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+    </row>
+    <row r="29" spans="1:5" ht="20" customHeight="1">
+      <c r="A29" s="35" t="s">
         <v>1050</v>
       </c>
-      <c r="B33" s="35" t="s">
+      <c r="B29" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="35" t="s">
+      <c r="C29" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="35" t="s">
+      <c r="D29" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E33" s="35" t="s">
-        <v>4811</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="78" customHeight="1">
-      <c r="A34" s="38" t="s">
-        <v>4812</v>
-      </c>
-      <c r="B34" s="36" t="s">
+      <c r="E29" s="35" t="s">
+        <v>4794</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="78" customHeight="1">
+      <c r="A30" s="38" t="s">
+        <v>4795</v>
+      </c>
+      <c r="B30" s="36" t="s">
         <v>4769</v>
       </c>
-      <c r="C34" s="36" t="s">
+      <c r="C30" s="36" t="s">
         <v>4770</v>
       </c>
-      <c r="D34" s="36" t="s">
+      <c r="D30" s="36" t="s">
         <v>4771</v>
       </c>
-      <c r="E34" s="36" t="s">
+      <c r="E30" s="36" t="s">
         <v>4772</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A35" s="44" t="s">
-        <v>4806</v>
+    <row r="31" spans="1:5" ht="93" hidden="1" customHeight="1">
+      <c r="A31" s="42" t="s">
+        <v>4789</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="108" hidden="1" customHeight="1">
+      <c r="A32" s="42" t="s">
+        <v>4789</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" s="39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="63" hidden="1" customHeight="1">
+      <c r="A33" s="42" t="s">
+        <v>4789</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" s="39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="123" hidden="1" customHeight="1">
+      <c r="A34" s="42" t="s">
+        <v>4789</v>
+      </c>
+      <c r="B34" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="303" hidden="1" customHeight="1">
+      <c r="A35" s="42" t="s">
+        <v>4789</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D35" s="39" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E35" s="39" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="108" hidden="1" customHeight="1">
-      <c r="A36" s="44" t="s">
-        <v>4806</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="93" hidden="1" customHeight="1">
+      <c r="A36" s="42" t="s">
+        <v>4789</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E36" s="39" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="63" hidden="1" customHeight="1">
-      <c r="A37" s="44" t="s">
-        <v>4806</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="78" hidden="1" customHeight="1">
+      <c r="A37" s="42" t="s">
+        <v>4789</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D37" s="39" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E37" s="39" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="123" hidden="1" customHeight="1">
-      <c r="A38" s="44" t="s">
-        <v>4806</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="93" hidden="1" customHeight="1">
+      <c r="A38" s="42" t="s">
+        <v>4789</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D38" s="39" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E38" s="39" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="303" hidden="1" customHeight="1">
-      <c r="A39" s="44" t="s">
-        <v>4806</v>
-      </c>
-      <c r="B39" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="C39" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="D39" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="E39" s="39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A40" s="44" t="s">
-        <v>4806</v>
-      </c>
-      <c r="B40" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="D40" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="E40" s="39" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="78" hidden="1" customHeight="1">
-      <c r="A41" s="44" t="s">
-        <v>4806</v>
-      </c>
-      <c r="B41" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="C41" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="E41" s="39" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A42" s="44" t="s">
-        <v>4806</v>
-      </c>
-      <c r="B42" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C42" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="D42" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="39" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A43" s="43" t="s">
-        <v>4806</v>
-      </c>
-      <c r="B43" s="37" t="s">
+    <row r="39" spans="1:5" ht="93" hidden="1" customHeight="1">
+      <c r="A39" s="41" t="s">
+        <v>4789</v>
+      </c>
+      <c r="B39" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="C43" s="37" t="s">
+      <c r="C39" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="D43" s="37" t="s">
+      <c r="D39" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="E43" s="37" t="s">
+      <c r="E39" s="37" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
     <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C18:E18"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_개발전달_데이터계약_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\전달\2026-10-19_연구소_식이데이터계약\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3448D1F5-D7D0-4EC9-A937-1CA55CE1DD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBC0B1C-BB74-49BA-9C94-6F9716E09D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="30" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15447" uniqueCount="4801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15442" uniqueCount="4796">
   <si>
     <t>항목</t>
   </si>
@@ -14489,21 +14489,6 @@
   </si>
   <si>
     <t>policy goal_history_days · 설정 CFG-065 · 설정파라미터 CFG-065 · 검증규칙 V-45</t>
-  </si>
-  <si>
-    <t>목표 단계 오르기 정책값</t>
-  </si>
-  <si>
-    <t>policy에 stage_up_window_days 7이 남아 있음. 실제 동작은 코드 상수(최근 4건 · 완료 3건 · 56일)로 계약과 같음</t>
-  </si>
-  <si>
-    <t>정책값을 계약에 맞춰 옮김: 최근 목표 4건 중 완료 3건 · 끝난 목표 3건 이상 · 56일 · 최근 2건 연속 미완료면 내림 · 관찰 중 축은 안 오름 · 개선 필요는 기본까지</t>
-  </si>
-  <si>
-    <t>policy · 설정파라미터 CFG-010 · CFG-011 · CFG-068 · CFG-069 · CFG-071</t>
-  </si>
-  <si>
-    <t>권장</t>
   </si>
   <si>
     <t>나머지</t>
@@ -14828,7 +14813,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「수정 요청」은 꼭 바꿀 것, 「권장」은 바꾸면 좋은 것입니다.</t>
+    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「수정 요청」은 꼭 바꿀 것입니다.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -14839,7 +14824,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -14976,12 +14961,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFC55911"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FF375623"/>
       <name val="Carlito"/>
     </font>
@@ -14993,7 +14972,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -15037,12 +15016,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -15095,7 +15068,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -15200,14 +15173,23 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -15218,22 +15200,10 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -18951,7 +18921,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="11.58203125" style="34" customWidth="1"/>
@@ -18963,40 +18933,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="44" t="s">
-        <v>4796</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
+      <c r="A1" s="47" t="s">
+        <v>4791</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
     </row>
     <row r="2" spans="1:5" ht="34" customHeight="1">
-      <c r="A2" s="46" t="s">
-        <v>4797</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
+      <c r="A2" s="45" t="s">
+        <v>4792</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
     </row>
     <row r="4" spans="1:5" ht="24" customHeight="1">
-      <c r="A4" s="47" t="s">
-        <v>4798</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
+      <c r="A4" s="43" t="s">
+        <v>4793</v>
+      </c>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
     </row>
     <row r="5" spans="1:5" ht="19" customHeight="1">
-      <c r="A5" s="46" t="s">
-        <v>4800</v>
-      </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
+      <c r="A5" s="45" t="s">
+        <v>4795</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
     </row>
     <row r="6" spans="1:5" ht="20" customHeight="1">
       <c r="A6" s="35" t="s">
@@ -19017,7 +18987,7 @@
     </row>
     <row r="7" spans="1:5" ht="48" customHeight="1">
       <c r="A7" s="38" t="s">
-        <v>4799</v>
+        <v>4794</v>
       </c>
       <c r="B7" s="36" t="s">
         <v>4777</v>
@@ -19032,415 +19002,398 @@
         <v>4780</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="48" customHeight="1">
+    <row r="8" spans="1:5" ht="78" hidden="1" customHeight="1">
       <c r="A8" s="40" t="s">
+        <v>4784</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>4781</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>4782</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>4783</v>
+      </c>
+      <c r="E8" s="37"/>
+    </row>
+    <row r="10" spans="1:5" ht="24" customHeight="1">
+      <c r="A10" s="43" t="s">
         <v>4785</v>
       </c>
-      <c r="B8" s="39" t="s">
-        <v>4781</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>4782</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>4783</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>4784</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="78" hidden="1" customHeight="1">
-      <c r="A9" s="41" t="s">
-        <v>4789</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>4786</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>4787</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>4788</v>
-      </c>
-      <c r="E9" s="37"/>
-    </row>
-    <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="A11" s="47" t="s">
-        <v>4790</v>
-      </c>
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-    </row>
-    <row r="12" spans="1:5" ht="20" customHeight="1">
-      <c r="B12" s="35" t="s">
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+    </row>
+    <row r="11" spans="1:5" ht="20" customHeight="1">
+      <c r="B11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C11" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+    </row>
+    <row r="12" spans="1:5" ht="18" customHeight="1">
+      <c r="B12" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1">
-      <c r="B13" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="50" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
+      <c r="B13" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1">
       <c r="B14" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
+        <v>6</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1">
       <c r="B15" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="43" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
+        <v>8</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1">
       <c r="B16" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1">
       <c r="B17" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
+        <v>12</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1">
       <c r="B18" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
+        <v>14</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1">
       <c r="B19" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
+        <v>16</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1">
       <c r="B20" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
+        <v>18</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>4786</v>
+      </c>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1">
       <c r="B21" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="43" t="s">
-        <v>4791</v>
-      </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
+        <v>19</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1">
       <c r="B22" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
+        <v>21</v>
+      </c>
+      <c r="C22" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1">
       <c r="B23" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-    </row>
-    <row r="24" spans="1:5" ht="18" customHeight="1">
-      <c r="B24" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="43" t="s">
+      <c r="C23" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-    </row>
-    <row r="25" spans="1:5" ht="33" customHeight="1">
-      <c r="B25" s="37" t="s">
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+    </row>
+    <row r="24" spans="1:5" ht="33" customHeight="1">
+      <c r="B24" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C24" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-    </row>
-    <row r="27" spans="1:5" ht="24" customHeight="1">
-      <c r="A27" s="47" t="s">
-        <v>4792</v>
-      </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-    </row>
-    <row r="28" spans="1:5" ht="34" customHeight="1">
-      <c r="A28" s="46" t="s">
-        <v>4793</v>
-      </c>
-      <c r="B28" s="46"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-    </row>
-    <row r="29" spans="1:5" ht="20" customHeight="1">
-      <c r="A29" s="35" t="s">
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+    </row>
+    <row r="26" spans="1:5" ht="24" customHeight="1">
+      <c r="A26" s="43" t="s">
+        <v>4787</v>
+      </c>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+    </row>
+    <row r="27" spans="1:5" ht="34" customHeight="1">
+      <c r="A27" s="45" t="s">
+        <v>4788</v>
+      </c>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+    </row>
+    <row r="28" spans="1:5" ht="20" customHeight="1">
+      <c r="A28" s="35" t="s">
         <v>1050</v>
       </c>
-      <c r="B29" s="35" t="s">
+      <c r="B28" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C28" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="35" t="s">
+      <c r="D28" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="E29" s="35" t="s">
-        <v>4794</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="78" customHeight="1">
-      <c r="A30" s="38" t="s">
-        <v>4795</v>
-      </c>
-      <c r="B30" s="36" t="s">
+      <c r="E28" s="35" t="s">
+        <v>4789</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="78" customHeight="1">
+      <c r="A29" s="38" t="s">
+        <v>4790</v>
+      </c>
+      <c r="B29" s="36" t="s">
         <v>4769</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C29" s="36" t="s">
         <v>4770</v>
       </c>
-      <c r="D30" s="36" t="s">
+      <c r="D29" s="36" t="s">
         <v>4771</v>
       </c>
-      <c r="E30" s="36" t="s">
+      <c r="E29" s="36" t="s">
         <v>4772</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A31" s="42" t="s">
-        <v>4789</v>
+    <row r="30" spans="1:5" ht="93" hidden="1" customHeight="1">
+      <c r="A30" s="41" t="s">
+        <v>4784</v>
+      </c>
+      <c r="B30" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="108" hidden="1" customHeight="1">
+      <c r="A31" s="41" t="s">
+        <v>4784</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C31" s="39" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D31" s="39" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E31" s="39" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="108" hidden="1" customHeight="1">
-      <c r="A32" s="42" t="s">
-        <v>4789</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="63" hidden="1" customHeight="1">
+      <c r="A32" s="41" t="s">
+        <v>4784</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C32" s="39" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D32" s="39" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E32" s="39" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="63" hidden="1" customHeight="1">
-      <c r="A33" s="42" t="s">
-        <v>4789</v>
+    <row r="33" spans="1:5" ht="123" hidden="1" customHeight="1">
+      <c r="A33" s="41" t="s">
+        <v>4784</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C33" s="39" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E33" s="39" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="123" hidden="1" customHeight="1">
-      <c r="A34" s="42" t="s">
-        <v>4789</v>
+    <row r="34" spans="1:5" ht="303" hidden="1" customHeight="1">
+      <c r="A34" s="41" t="s">
+        <v>4784</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D34" s="39" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E34" s="39" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="303" hidden="1" customHeight="1">
-      <c r="A35" s="42" t="s">
-        <v>4789</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="93" hidden="1" customHeight="1">
+      <c r="A35" s="41" t="s">
+        <v>4784</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D35" s="39" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E35" s="39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A36" s="42" t="s">
-        <v>4789</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="78" hidden="1" customHeight="1">
+      <c r="A36" s="41" t="s">
+        <v>4784</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C36" s="39" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E36" s="39" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="78" hidden="1" customHeight="1">
-      <c r="A37" s="42" t="s">
-        <v>4789</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="93" hidden="1" customHeight="1">
+      <c r="A37" s="41" t="s">
+        <v>4784</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D37" s="39" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E37" s="39" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A38" s="42" t="s">
-        <v>4789</v>
-      </c>
-      <c r="B38" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="D38" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" s="39" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A39" s="41" t="s">
-        <v>4789</v>
-      </c>
-      <c r="B39" s="37" t="s">
+      <c r="A38" s="40" t="s">
+        <v>4784</v>
+      </c>
+      <c r="B38" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="37" t="s">
+      <c r="C38" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="D39" s="37" t="s">
+      <c r="D38" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="E39" s="37" t="s">
+      <c r="E38" s="37" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
